--- a/Vegetation Cover and Food Availability Studies/Habitat check list_mc_yp.xlsx
+++ b/Vegetation Cover and Food Availability Studies/Habitat check list_mc_yp.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28526"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://sinet-my.sharepoint.com/personal/pangy_si_edu/Documents/Bustard/01_Data/Reneco/Vegetation Cover and Food Availability Studies/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://sinet-my.sharepoint.com/personal/pangy_si_edu/Documents/Bustard/07_Bustard-Project/Vegetation Cover and Food Availability Studies/"/>
     </mc:Choice>
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{47683FE4-2BE9-422A-92A5-8E292FFB587A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3072" yWindow="3072" windowWidth="23040" windowHeight="12120" tabRatio="599" xr2:uid="{8B685812-31A7-4410-A581-327840EED513}"/>
+    <workbookView minimized="1" xWindow="384" yWindow="384" windowWidth="23040" windowHeight="13560" tabRatio="599" xr2:uid="{8B685812-31A7-4410-A581-327840EED513}"/>
   </bookViews>
   <sheets>
     <sheet name="habitat" sheetId="2" r:id="rId1"/>
